--- a/bbc_news.xlsx
+++ b/bbc_news.xlsx
@@ -446,7 +446,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Andy Burnham said he would seek to enter any potential Labour leadership contest should he win the Makerfield by-election on 18 June.
+The Greater Manchester mayor made clear his ambitions as he appeared alongside four other candidates during a BBC Question Time special in the constituency.
+Reform UK candidate Robert Kenyon said there was a need for a "big move away from career politicians" and warned against using Makerfield as a "stepping stone".
+Prime Minister Sir Keir Starmer has defied calls from some Labour MPs to step down after poor election results last month. No formal challenge has been launched against him.
+A No 10 spokesperson said: "The prime minister will not walk away from the mandate he was given just two years ago to build a stronger, fairer Britain."</t>
         </is>
       </c>
     </row>
@@ -463,7 +467,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Andrew Mountbatten-Windsor received an undisclosed rental income from sub-letting three cottages on the Royal Lodge estate that he leased from the Crown Estate, the public spending watchdog has revealed.
+The National Audit Office (NAO) report also revealed that the King pays the rent for accommodation in royal palaces for Mountbatten-Windsor's daughters Princesses Eugenie and Beatrice, who are not working royals.
+It is the first report into royal residences in 20 years and shows Mountbatten-Windsor and his family and staff had 12 properties, owned by the Crown Estate or the Royal Household.
+A Buckingham Palace spokesman said the report was "in line with the Royal Household's commitment to transparency".
+The watchdog report into royal residences shows that Princess Eugenie has a property in Kensington Palace and Princess Beatrice in St James's Palace.</t>
         </is>
       </c>
     </row>
@@ -480,7 +488,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Artificial intelligence has been used to develop a "fundamentally new" type of vaccine that could protect against large swathes of viruses and prevent pandemics, say researchers.
+The team at the University of Cambridge say it is the first time a vaccine's key component has been designed entirely by AI and then trialled in people.
+The vaccine was engineered to work on all coronaviruses which would include all Covid variants and viruses that infect animals, but could start the next pandemic.
+The work is still in the early stages, but the team is already developing separate vaccines that could tackle flu and Ebola.
+Vaccines teach our bodies how to spot an infection to increase our chances of fighting it off.</t>
         </is>
       </c>
     </row>
@@ -497,7 +509,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>A quarter of all babies in England are now delivered by emergency caesarean operations, BBC analysis shows - marking a significant rise over the last five years.
+The unplanned surgeries have increased by eight percentage points, while the rate of elective caesareans has also increased.
+At the same time, the rate of vaginal births without instruments has fallen - from more than half of all deliveries to 43%.
+Prof Marian Knight, director of the National Perinatal Epidemiology Unit, which researches the care of women and babies in pregnancy and birth, says the rise represents a "total change in how women give birth" in England, and that it has not been replicated in other European countries.
+The NHS does not publish data on why an emergency C-section is performed, and experts say there is no single, clear explanation for the increase.</t>
         </is>
       </c>
     </row>
@@ -514,7 +530,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>In the year since US President Donald Trump announced plans to build a new ballroom at the White House, the proposals have grown to include a rooftop "drone port", an underground hospital and "top secret" military facilities - and the estimated price has doubled to $400m (£300m).
+Despite promises from Trump that the project wouldn't cost US taxpayers any money, Republicans have requested additional funds from Congress for security around the complex - at a time when Americans are struggling with rising living costs linked to the Iran war.
+The president indicated from the outset that the new ballroom is needed to "accommodate people for grand parties, State Visits", and more recently said it is "vital for National Security".
+BBC Verify has examined how the biggest change to the White House in decades has transformed over the past year.
+On 6 June last year, Trump announced on his social media platform Truth Social that he had inspected the site where a new ballroom would be built, promising it would "go up quickly" and would be "very much in keeping with the magnificent White House itself".</t>
         </is>
       </c>
     </row>
@@ -531,7 +551,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">Three members of the Royal Navy who died in a helicopter crash during a training exercise have been named.
+The crew were Lt Cdr Chris Gayson, 42, Lt Lily-Mae Fisher, 31, who was Britain's only female Royal Navy commando, and Petty Officer Owen Green, 24, the Ministry of Defence (MoD) has confirmed. All three were based at RNAS Yeovilton, Somerset.
+Their families all paid tribute, while the military described them as "deeply capable and professional aviators" and "cherished members" of the Commando Helicopter Force. 
+Gayson, Fisher and Green died on board a Merlin Mk4 helicopter that crashed at about 03:45 BST on Wednesday near Okehampton, Devon.
+Gayson's family said he was "an extremely kind and gentle family man who loved his entire family dearly".  </t>
         </is>
       </c>
     </row>
@@ -548,7 +572,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Former police officer Christi Hill has told BBC Verify she has been forced into hiding and is fearful for her safety after she and another officer were misidentified on social media as being involved in the arrest of Henry Nowak.
+Bodycam footage released this week shows 18-year-old Henry being handcuffed by officers as he repeatedly said he couldn't breathe. The other officer, PC Tristan Parsons was out of the country - and Christi Hill had left the force more than a year before the incident. Kayleen Devlin reports.
+Produced by Aisha Sembhi. Graphics by Sally Nicholls and Mark Edwards. Reporting by Kevin Nguyen.
+The pair are filmed swimming in the water at Blashford Lakes Nature Reserve, near Ringwood.
+James Bruton builds all of his inventions in a secret location in Hampshire and posts videos on YouTube.</t>
         </is>
       </c>
     </row>
@@ -565,7 +593,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Sir Keir Starmer has paid tribute to Henry Nowak saying the 18-year-old "deserves a legacy that goes beyond this awful tragedy". 
+The prime minister said he was "profoundly humbled" to meet the student's family in Downing Street on Thursday and he was determined to "prevent other families from suffering such a devastating loss".
+There has been widespread outrage after bodycam footage showed police putting the Southampton University student in handcuffs as he lay dying, after his killer Vickrum Digwa falsely claimed he had been the victim of a racist attack.
+Sir Keir said there were "difficult questions that need to be answered about the way the police handled Henry's murder".
+Footage of the teenager's arrest showed him repeatedly tell officers he had been stabbed, with one replying: "I don't think so mate".</t>
         </is>
       </c>
     </row>
@@ -582,7 +614,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Conflict over identity politics in the UK could lead to civil war in the long term, Kemi Badenoch has said.
+In an interview for a BBC Radio 4 documentary, England's Identity Crisis, the Conservative leader warned of rising tensions as groups on the left and the right direct "more and more hostility" towards people of every ethnicity.
+The Conservative leader censured parties that use the political conflict to target voters from one community, an ingredient that she says could lead to an eventual civil war.
+The interview was conducted before political tension erupted over policing, following the release of bodycam footage showing the handcuffing of murdered teenager Henry Nowak as he lay dying.
+Both Prime Minister Sir Keir Starmer and Badenoch have called for politicians not to stoke division following the outcry about the teenager's murder, and subsequent protests on the streets of Southampton.</t>
         </is>
       </c>
     </row>
@@ -599,7 +635,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Anthropic co-founder Jack Clark has called for the ability to slow progression of artificial intelligence (AI), warning the technology is nearing a point where it could develop without human input.
+"You want the option to be able to take your foot off the gas and put your foot on the brake", Clark told BBC Newsnight. "Right now, it's like the AI industry has a gas pedal, but it doesn't have a brake pedal."
+He stressed people, through government policy, need to keep control of AI systems, which will only get more powerful and have broader impacts on society.
+"The world needs to do some thinking and we need to eventually develop some new regulations that allow us to be confident in these systems," he said.
+Already, Anthropic's popular chatbot Claude is operating on code of which 80% the system wrote itself. Getting to 100% is possible within two years, Clark said, and "would have huge implications".</t>
         </is>
       </c>
     </row>
@@ -616,7 +656,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">Volodymyr Zelensky has called for a face-to-face meeting between himself and Vladimir Putin in a renewed bid to end the war.
+In an open letter to the Russian president, the Ukrainian leader said it would be "wrong to simply wait" until the war in Europe becomes the focus of the US's attention once more, adding peace could only come "through direct engagement between" Ukraine and Russia.
+He also called for a full ceasefire for the duration of proposed negotiations - something Putin ruled out earlier on Thursday.
+US President Donald Trump said on Thursday he thought "it would be great" if the two leaders met.
+The Kremlin confirmed it had received the letter and Putin would be briefed on it. </t>
         </is>
       </c>
     </row>
@@ -633,7 +677,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The world's coastal mangrove forests, which protect millions of people from storms - and soak up vast amounts of planet-warming gases - are staging an unexpected comeback, scientists find.
+For decades these swampy trees had been declining rapidly as they were cleared for fish farms and housing.
+But a new study shows that since 2010 the world has been gaining more mangroves than it has been losing - driven by stronger legal protections and increased public awareness of their importance, sparked by disasters such as the 2004 Indian Ocean tsunami.
+The researchers say the key factor though is the remarkable capacity of these forests to regenerate naturally once humans stop chopping them down.
+Mangroves are one of the world's unsung environmental heroes.</t>
         </is>
       </c>
     </row>
@@ -650,7 +698,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The pop graveyard is full of bands who fell out, melted down and broke up.
+British boyband Five split after their backstage arguments escalated into fist fights. A row about a jacket sparked All Saints deciding to part ways. Oasis took a 16-year hiatus after Liam Gallagher threw a plum at his brother Noel.
+But it's rare to hear a group talk about resolving their problems. So I've a huge amount of admiration for the latest album by Korean girl group Le Sserafim.
+Sitting in the middle of the tracklist is a song called Need Your Company, which details the history of friction between New York-born member Huh Yunjin, and her bandmate Kim Chaewon.
+"Is friendship all just for show?" they sing over a melancholy guitar line. "I really wanna trust you... no matter how you hurt me."</t>
         </is>
       </c>
     </row>
@@ -667,7 +719,9 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">Sign up for our morning newsletter and get BBC News in your inbox.
+Copyright 2026 BBC. All rights reserved. The BBC is not responsible for the content of external sites. Read about our approach to external linking.
+ </t>
         </is>
       </c>
     </row>
@@ -684,7 +738,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>This week, the US House of Representatives voted to end the war with Iran, social media star KSI quit YouTube collective The Sidemen, and Amazon founder Jeff Bezos's rocket blew up on the launch pad.
+But how much attention did you pay to what else happened in the world over the past seven days?
+Quiz collated by Ben Fell.
+Fancy some more? Try last week's quiz, or have a go at something from the archives.
+Copyright 2026 BBC. All rights reserved. The BBC is not responsible for the content of external sites. Read about our approach to external linking.</t>
         </is>
       </c>
     </row>
@@ -701,7 +759,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Single 20-somethings need AI to start conversations on dating apps because they lack the confidence of older generations, says the boss of Hinge.
+Jackie Jantos told the BBC Gen Z daters "absolutely want love" but were "struggling to have the confidence to put themselves out there" as they socialise less in person.
+She defended Hinge's AI feature which creates prompts to start chatting with a match as "not about writing words for you" but "helping you express who you are".
+Hinge has continued to grow its UK users despite some relationship experts warning of "dating app burnout" and a return to more organic in person meetings.
+Founded in 2012 and owned by Match Group, which also owns Tinder and Match.com, Hinge has built its brand around the slogan "designed to be deleted".</t>
         </is>
       </c>
     </row>
@@ -718,126 +780,158 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">The Lifetime ISA (LISA) was set up in 2017 to help people save for retirement or purchase a first home costing up to £450,000. First-time buyers can put aside £4,000 a year and get an annual government bonus of 25%.
+But if savers are unable to find a property below the cap and need to withdraw the money, they face a financial penalty which costs them 6.25% of their savings.
+With the average first-time buyer now spending £463,000 in London, the scheme's property price cap is seen by many as being out of step with the capital's housing market.
+Based on figures from September 2025, BBC analysis found that the median LISA user could afford:
+In 13 boroughs, the median price for all types of properties was above £450,000. </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kate hugs mum ringing 'end of cancer treatment' bell</t>
+          <t>Mount Everest climber recounts moment he lost guide who survived alone for six days</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cq5p52l2xjjo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/cn9p91295q8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>A former British soldier has recounted the moment he became separated from a Nepali mountain guide as they were descending Mount Everest.
+Dawa Sherpa was found alive on Thursday, after six days in what's known as the "death zone". Climber Chris Thrall said that at first, it was impossible to believe Sherpa had survived against the odds.
+Thrall told BBC's Newshour: "It's kind of crazy one minute to be fighting back tears with his daughter, and then the next minute to see him crawling into town. It's absolutely amazing, beyond words".
+Thrall had last seen Dawa Sherpa sitting on his backpack to have a short rest as they made their way back towards base camp after arduous days of climbing. 
+Thrall passed the guide, also known as Hillary Dawa Sherpa after famed mountaineer Edmund Hillary.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mount Everest climber recounts moment he lost guide who survived alone for six days</t>
+          <t>Hezbollah rejects renewed ceasefire agreed by Israel and Lebanon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cn9p91295q8o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/c052343r812o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The Lebanese armed group Hezbollah has emphatically rejected the terms of a US-backed ceasefire between Israel and Lebanon.
+In a strongly worded statement, the Iran-backed group's leader Naim Qassem said negotiations had been "futile" and "humiliating" for Lebanon, and rejected categorically by "broad segments of the Lebanese people". 
+It comes after Israel and Lebanon announced a renewal of their fragile ceasefire with the creation of "pilot" security zones inside Lebanon in which Hezbollah operatives would be banned. It also required Hezbollah to stop attacking Israel.
+Donald Trump later said he had spoken to Hezbollah and Israeli Prime Minister Benjamin Netanyahu and progress was being made.
+Trump added "I think you're going to see things happen over there".</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liverpool appoint Andoni Iraola as head coach</t>
+          <t>Kate hugs mum ringing 'end of cancer treatment' bell</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cqjpkgx7084o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/cq5p52l2xjjo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The Princess of Wales has hugged and congratulated a young mother celebrating the completion of her course of chemotherapy.
+Kate, who revealed at the start of last year she was herself in remission from cancer, joined Claire Lorente as the 30-year-old rang the "end of treatment bell" at The Christie hospital in Manchester in front of family members and staff.
+The princess was visiting the specialist cancer unit to see the wide range of holistic care that is offered there.
+Kate told Claire: "Well done you - what a journey! It's been a tough one, yeah? You have done brilliantly. Well done."
+Kate also embraced Claire's partner Pablo and said: "Well done. It's just as hard for the family and loved ones."</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Man shot with crossbow on university campus</t>
+          <t>Liverpool appoint Andoni Iraola as head coach</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cn4p4yllq1lo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/sport/football/articles/cqjpkgx7084o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Andoni Iraola won seven caps for Spain in a playing career spent mainly at Athletic Club
+Andoni Iraola says he understands "what is expected" but is ready for the challenge ahead after Liverpool confirmed him as their new head coach.
+Iraola, 43, has signed a two-year deal to replace Arne Slot, who was sacked on Saturday - a year after guiding the club to the Premier League title.
+Former Bournemouth manager Iraola joins after delivering the Cherries' finest top-flight season to date, finishing in sixth place.
+That was only one position and three points behind Liverpool and gave Bournemouth a place in next season's Europa League.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ex-wife of Dubai ruler's nephew in custody, prosecutors say</t>
+          <t>Steven Spielberg believes we will discover aliens in our lifetime</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cx2124zylxno?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/c042wqk0xdzo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>For more than 40 years, Steven Spielberg has been asking audiences the same question: what if we're not alone?
+From the friendly alien at the heart of E.T. to the mysterious visitors in Close Encounters of the Third Kind, some of his most celebrated films have explored humanity's fascination with life beyond Earth.
+Now, the Oscar-winning director is returning to that theme once again with Disclosure Day, a sci-fi thriller starring Emily Blunt, Josh O'Connor, Colman Domingo, Colin Firth and Eve Hewson.
+The film imagines a world on the brink of a revelation: proof that non-human intelligence exists and has been hidden in plain sight. 
+At the centre of the story are Blunt's character, meteorologist Margaret Fairchild, and O'Connor's Daniel Kellner, a cybersecurity expert who uncovers evidence of a long-running cover-up and finds himself pursued as governments and powerful corporations race to contain the truth.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hezbollah rejects renewed ceasefire agreed by Israel and Lebanon</t>
+          <t>Man shot with crossbow on university campus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c052343r812o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/cn4p4yllq1lo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>A 21-year-old man has been arrested on suspicion of attempted murder after a member of staff at the University of Surrey was shot with a crossbow. 
+Surrey Police said officers were called to reports of a man in his 50s being shot with the weapon at Manor Park Student Village, Guildford, at around 10:00 BST on Thursday. 
+A former student at the university has been arrested and is in custody, according to police. 
+The University of Surrey said a member of its campus safety team had been "seriously injured". 
+Officers have said they are not treating it as a terror-related incident.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Steven Spielberg believes we will discover aliens in our lifetime</t>
+          <t>Ex-wife of Dubai ruler's nephew in custody, prosecutors say</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c042wqk0xdzo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/news/articles/cx2124zylxno?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The ex-wife of a nephew of the ruler of Dubai has been taken into custody, authorities have said.
+Dubai Public Prosecution told the BBC that Zenab Javadli was detained following a complaint made by the father of her three children - her former husband, Sheikh Saeed bin Maktoum bin Rashid Al Maktoum.
+He alleged that she had abducted the children during a court-approved visitation session.
+Javadli's family and friends had lost contact with her since Tuesday night and had raised the alarm over her whereabouts.
+For almost two days, no news was received as to where Javadli or her children had gone.</t>
         </is>
       </c>
     </row>
@@ -854,7 +948,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>The BBC News app is available for Android and iOS devices
+With the latest news and analysis from our journalists around the world and the unique human stories behind current events, we've got the best of our journalism in one place on the BBC News app.
+Click here, external to download the BBC News app from the App Store for iPhone, iPad and iPod Touch.
+Click here, external to download the BBC News app from Google Play for Android devices.
+If you're outside the UK, you can download the BBC app here, external.</t>
         </is>
       </c>
     </row>
@@ -871,7 +969,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">
+Use BBC.com or the new BBC App to listen to BBC podcasts, Radio 4 and the World Service outside the UK.
+Find out how to listen to other BBC stations
+News,·03 Jun 2026,·43 mins,·
+Available for over a year</t>
         </is>
       </c>
     </row>
@@ -888,7 +990,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">
+Use BBC.com or the new BBC App to listen to BBC podcasts, Radio 4 and the World Service outside the UK.
+Find out how to listen to other BBC stations
+News,·29 May 2026,·31 mins
+Available for over a year</t>
         </is>
       </c>
     </row>
@@ -905,7 +1011,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">
+With Beckham, Rooney, Ferdinand and Cole on the team, the 2006 World Cup was supposed to be England's moment. So why did the dream end in on-field agony and off-field acrimony? More</t>
         </is>
       </c>
     </row>
@@ -922,7 +1029,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">
+Emma Barnett shares her struggle with endometriosis, shedding light on her own worsening illness and other women’s stories, exposing a neglected disease which has no known cure. More</t>
         </is>
       </c>
     </row>
@@ -939,7 +1047,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>This video can not be played
+How's that for a return?! Robinson takes three wickets in first over in two years
+Paul Farbrace has a gag about how Ollie Robinson came to be Sussex captain.
+Farbrace, the Sussex head coach, realised he had not got his step-son a decent Christmas present, so offered him the county captaincy instead.
+It's a nice line. The truth is that Sussex wanted to get the absolute best out of their champion bowler and reasoned it would come through more responsibility.</t>
         </is>
       </c>
     </row>
@@ -956,7 +1068,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Andoni Iraola won seven caps for Spain in a playing career spent mainly at Athletic Club
+Andoni Iraola says he understands "what is expected" but is ready for the challenge ahead after Liverpool confirmed him as their new head coach.
+Iraola, 43, has signed a two-year deal to replace Arne Slot, who was sacked on Saturday - a year after guiding the club to the Premier League title.
+Former Bournemouth manager Iraola joins after delivering the Cherries' finest top-flight season to date, finishing in sixth place.
+That was only one position and three points behind Liverpool and gave Bournemouth a place in next season's Europa League.</t>
         </is>
       </c>
     </row>
@@ -973,7 +1089,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Maja Chwalinska is making her first appearance in the French Open main draw, having lost in qualifying in 2021, 2023 and 2025
+After coming through her darkest hours, surprise French Open finalist Maja Chwalinska visited a tattoo parlour.
+A tiny word - 'free' - was etched on to the 24-year-old qualifier's left hand.
+Poland's Chwalinska, who is one win from joining Britain's Emma Raducanu and becoming only the second qualifier to lift a Grand Slam title, would not be drawn on why she chose that tattoo.
+"I will keep it to myself. You can make your own stories," Chwalinska said.</t>
         </is>
       </c>
     </row>
@@ -990,7 +1110,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Robbie Keane has been heavily linked with Celtic since resigning from his post at Budapest club Ferencvaros
+Several Celtic supporters clubs have put their name to a statement opposing the potential appointment of Robbie Keane as manager because of the Irishman's previous role as Maccabi Tel Aviv head coach.
+Recent reports, external suggest Keane, 45, has had talks with the Scottish champions' principal shareholder Dermot Desmond.
+The Republic of Ireland's record goalscorer has won league titles in Israel and Hungary as a manager.
+However, his decision to stay in Israel after the conflict in Gaza began drew criticism in his homeland and has turned a section of the Celtic fanbase against him.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1131,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>This video can not be played
+Hunter Bell fights back to win 1500m in Rome
+World indoor champions Molly Caudery and Georgia Hunter Bell triumphed in the pole vault and 1500m at the Diamond League meeting in Rome.
+Two-time world indoor champion Caudery sealed the pole vault title with a clearance of 4.80m.
+Track star Hunter Bell, who took a first world title in Torun in March, broke away from the leading pack to win her event in three minutes 58.63 seconds at the Stadio Olimpico.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1152,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t>Fifa promised a sold-out World Cup but there are still tickets available for over half the games
+Falling prices, fluctuating availability and a lack of clarity. With one week to go until the 2026 World Cup kicks off, many questions remain unanswered about match tickets.
+Fifa promised the event would be sold out, but there are thousands of tickets available for sale across several platforms.
+BBC Sport has found tickets for matches involving the smaller nations are now available well below face value - across Fifa's own resale site and secondary marketplaces.
+World football's governing body has itself been accused of dumping inventory it now cannot sell on SeatGeek.</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1173,10 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>本文取得失敗</t>
+          <t xml:space="preserve">There was an error
+After two years away, Ollie Robinson marked his return to Test cricket with four wickets as New Zealand closed day one of the opening Test against England on 61-6, still trailing the home side by 79 runs in the first innings at Lord's.
+READ MORE Stunning Robinson return gives life to England
+</t>
         </is>
       </c>
     </row>
